--- a/samples/ss_paiton123_ingest.xlsx
+++ b/samples/ss_paiton123_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,65 +535,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -632,24 +637,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -685,41 +691,46 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>PITON7</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>PITON5</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>2 IBT x 500 MVA (unit 1,3)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -755,41 +766,46 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>PITON7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>PITON5</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>1 IBT x 500 MVA (unit 2); beban &gt;90%</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -822,30 +838,31 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>bus A1/B1 - A2/B2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -878,34 +895,35 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>60/20/60 MVA</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -938,34 +956,35 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>20/20/60 MVA</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -998,34 +1017,35 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>30/60/30 MVA + 25 MVAR + SVC (+50/-25 MVAR)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1058,34 +1078,35 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>60/60/60 MVA</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1118,34 +1139,35 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>4x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1178,30 +1200,31 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>60 MVA + 2x25 MVAR</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1234,34 +1257,35 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>60 MVA</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1294,34 +1318,35 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>3x60 MVA + 50 MVAR</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1354,30 +1379,31 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>2x60 MVA</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1410,30 +1436,31 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>25 MVA</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1466,30 +1493,31 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>1x30 MW</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1522,38 +1550,39 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>ujung Kabel Laut SKLT Jawa-Bali</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_paiton123_ingest.xlsx
+++ b/samples/ss_paiton123_ingest.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/samples/ss_paiton123_ingest.xlsx
+++ b/samples/ss_paiton123_ingest.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 1,3 Paiton 500/150 kV</t>
+          <t>IBT 1 Paiton 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT x 500 MVA (unit 1,3)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -738,12 +734,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 2 Paiton 500/150 kV</t>
+          <t>IBT 3 Paiton 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IBT 2 PITON7</t>
+          <t>IBT 3 PITON7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -761,7 +757,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -778,11 +774,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>1 IBT x 500 MVA (unit 2); beban &gt;90%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -797,7 +789,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -813,35 +805,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Paiton (bus 150 kV)</t>
+          <t>IBT 2 Paiton 500/150 kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>IBT 2 PITON7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>PITON7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>PITON5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>bus A1/B1 - A2/B2</t>
+          <t>1 IBT x 500 MVA (unit 2); beban &gt;90%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -853,10 +859,14 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -870,12 +880,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Situbondo</t>
+          <t>Paiton (bus 150 kV)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>STBND</t>
+          <t>PITON5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -884,7 +894,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -898,7 +908,7 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>60/20/60 MVA</t>
+          <t>bus A1/B1 - A2/B2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -910,14 +920,10 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -931,12 +937,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bondowoso</t>
+          <t>Situbondo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BDWSO</t>
+          <t>STBND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -945,7 +951,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -959,7 +965,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20/20/60 MVA</t>
+          <t>60/20/60 MVA</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -976,7 +982,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -992,12 +998,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Banyuwangi</t>
+          <t>Bondowoso</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BWANG</t>
+          <t>BDWSO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1020,7 +1026,7 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>30/60/30 MVA + 25 MVAR + SVC (+50/-25 MVAR)</t>
+          <t>20/20/60 MVA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1037,7 +1043,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1053,12 +1059,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Genteng</t>
+          <t>Banyuwangi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GTENG</t>
+          <t>BWANG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1067,7 +1073,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1081,7 +1087,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>60/60/60 MVA</t>
+          <t>30/60/30 MVA + 25 MVAR + SVC (+50/-25 MVAR)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1098,7 +1104,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1114,12 +1120,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jember</t>
+          <t>Genteng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JMBER</t>
+          <t>GTENG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1128,7 +1134,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1142,7 +1148,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4x60 MVA + 50 MVAR</t>
+          <t>60/60/60 MVA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1175,12 +1181,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Puger</t>
+          <t>Jember</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PUGER</t>
+          <t>JMBER</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1189,7 +1195,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1203,7 +1209,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>60 MVA + 2x25 MVAR</t>
+          <t>4x60 MVA + 50 MVAR</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1215,10 +1221,14 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1232,12 +1242,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tanggul</t>
+          <t>Puger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TNGUL</t>
+          <t>PUGER</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1260,7 +1270,7 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>60 MVA</t>
+          <t>60 MVA + 2x25 MVAR</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1272,14 +1282,10 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1293,12 +1299,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lumajang</t>
+          <t>Tanggul</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LJANG</t>
+          <t>TNGUL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1307,7 +1313,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1321,7 +1327,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3x60 MVA + 50 MVAR</t>
+          <t>60 MVA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1354,12 +1360,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kraksaan</t>
+          <t>Lumajang</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KRSAN</t>
+          <t>LJANG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1368,7 +1374,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1382,7 +1388,7 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2x60 MVA</t>
+          <t>3x60 MVA + 50 MVAR</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1394,10 +1400,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -1411,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gending</t>
+          <t>Kraksaan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GDING</t>
+          <t>KRSAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1439,7 +1449,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>25 MVA</t>
+          <t>2x60 MVA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1468,21 +1478,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PLTP Ijen</t>
+          <t>Gending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KIT_IJEN</t>
+          <t>GDING</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1496,7 +1506,7 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1x30 MW</t>
+          <t>25 MVA</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1525,17 +1535,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gilimanuk (Subsistem Bali)</t>
+          <t>PLTP Ijen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GLMUK</t>
+          <t>KIT_IJEN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1553,7 +1563,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ujung Kabel Laut SKLT Jawa-Bali</t>
+          <t>1x30 MW</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -1562,27 +1572,84 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Gilimanuk (Subsistem Bali)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GLMUK</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ujung Kabel Laut SKLT Jawa-Bali</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Jawa Timur</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Jawa Timur</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2787,12 +2854,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[N-1] Terjadi ketidakseimbangan pembebanan Kabel Laut SKTT 150 kV Banyuwangi-Gilimanuk 1,2,3,4</t>
+          <t>[BELUM_DITETAPKAN] Terjadi ketidakseimbangan pembebanan Kabel Laut SKTT 150 kV Banyuwangi-Gilimanuk 1,2,3,4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
